--- a/E-commerce_Retail_Sales/BlueJay_Natural_Gas_Company_Financials_Analysis/Bluejay_Natural_Gas_Solution_Midterm.xlsx
+++ b/E-commerce_Retail_Sales/BlueJay_Natural_Gas_Company_Financials_Analysis/Bluejay_Natural_Gas_Solution_Midterm.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDEDE32E-77E3-4A12-9C29-BC3A3363DC56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A02BA1B3-5ABB-40A5-8900-0DA1E43E67C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{EB30C26F-4571-5447-8EFE-CD622A342A0B}"/>
   </bookViews>
@@ -12,10 +12,57 @@
     <sheet name="Approved Line Charts" sheetId="6" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="solver_eng" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_adj" localSheetId="0" hidden="1">'Project Model'!$K$19:$K$23,'Project Model'!$K$26:$K$29,'Project Model'!$K$32:$K$34,'Project Model'!$C$60:$J$71</definedName>
+    <definedName name="solver_cvg" localSheetId="0" hidden="1">0.0001</definedName>
+    <definedName name="solver_drv" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_eng" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_est" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_itr" localSheetId="0" hidden="1">2147483647</definedName>
+    <definedName name="solver_lhs1" localSheetId="0" hidden="1">'Project Model'!$C$60:$J$71</definedName>
+    <definedName name="solver_lhs2" localSheetId="0" hidden="1">'Project Model'!$C$72:$J$72</definedName>
+    <definedName name="solver_lhs3" localSheetId="0" hidden="1">'Project Model'!$C$79</definedName>
+    <definedName name="solver_lhs4" localSheetId="0" hidden="1">'Project Model'!$D$38:$F$38</definedName>
+    <definedName name="solver_lhs5" localSheetId="0" hidden="1">'Project Model'!$G$38</definedName>
+    <definedName name="solver_lhs6" localSheetId="0" hidden="1">'Project Model'!$K$19:$K$23</definedName>
+    <definedName name="solver_lhs7" localSheetId="0" hidden="1">'Project Model'!$K$26:$K$29</definedName>
+    <definedName name="solver_lhs8" localSheetId="0" hidden="1">'Project Model'!$K$32:$K$34</definedName>
+    <definedName name="solver_lhs9" localSheetId="0" hidden="1">'Project Model'!$K$60:$K$71</definedName>
+    <definedName name="solver_mip" localSheetId="0" hidden="1">2147483647</definedName>
+    <definedName name="solver_mni" localSheetId="0" hidden="1">30</definedName>
+    <definedName name="solver_mrt" localSheetId="0" hidden="1">0.075</definedName>
+    <definedName name="solver_msl" localSheetId="0" hidden="1">2</definedName>
     <definedName name="solver_neg" localSheetId="0" hidden="1">1</definedName>
-    <definedName name="solver_num" localSheetId="0" hidden="1">0</definedName>
-    <definedName name="solver_opt" localSheetId="0" hidden="1">'Project Model'!$N$14</definedName>
+    <definedName name="solver_nod" localSheetId="0" hidden="1">2147483647</definedName>
+    <definedName name="solver_num" localSheetId="0" hidden="1">9</definedName>
+    <definedName name="solver_nwt" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_opt" localSheetId="0" hidden="1">'Project Model'!$I$38</definedName>
+    <definedName name="solver_pre" localSheetId="0" hidden="1">0.000001</definedName>
+    <definedName name="solver_rbv" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_rel1" localSheetId="0" hidden="1">5</definedName>
+    <definedName name="solver_rel2" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_rel3" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_rel4" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_rel5" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_rel6" localSheetId="0" hidden="1">5</definedName>
+    <definedName name="solver_rel7" localSheetId="0" hidden="1">5</definedName>
+    <definedName name="solver_rel8" localSheetId="0" hidden="1">5</definedName>
+    <definedName name="solver_rel9" localSheetId="0" hidden="1">1</definedName>
+    <definedName name="solver_rhs1" localSheetId="0" hidden="1">"binary"</definedName>
+    <definedName name="solver_rhs2" localSheetId="0" hidden="1">'Project Model'!$C$74:$J$74</definedName>
+    <definedName name="solver_rhs3" localSheetId="0" hidden="1">8</definedName>
+    <definedName name="solver_rhs4" localSheetId="0" hidden="1">'Project Model'!$N$6</definedName>
+    <definedName name="solver_rhs5" localSheetId="0" hidden="1">'Project Model'!$N$5</definedName>
+    <definedName name="solver_rhs6" localSheetId="0" hidden="1">"binary"</definedName>
+    <definedName name="solver_rhs7" localSheetId="0" hidden="1">"binary"</definedName>
+    <definedName name="solver_rhs8" localSheetId="0" hidden="1">"binary"</definedName>
+    <definedName name="solver_rhs9" localSheetId="0" hidden="1">'Project Model'!$M$60:$M$71</definedName>
+    <definedName name="solver_rlx" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_rsd" localSheetId="0" hidden="1">0</definedName>
+    <definedName name="solver_scl" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_sho" localSheetId="0" hidden="1">2</definedName>
+    <definedName name="solver_ssz" localSheetId="0" hidden="1">100</definedName>
+    <definedName name="solver_tim" localSheetId="0" hidden="1">2147483647</definedName>
+    <definedName name="solver_tol" localSheetId="0" hidden="1">0.01</definedName>
     <definedName name="solver_typ" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_val" localSheetId="0" hidden="1">0</definedName>
     <definedName name="solver_ver" localSheetId="0" hidden="1">3</definedName>
@@ -74,7 +121,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="78">
   <si>
     <t>Project Index</t>
   </si>
@@ -231,6 +278,84 @@
   <si>
     <t>Total Approved NPV:</t>
   </si>
+  <si>
+    <t>Manager 1</t>
+  </si>
+  <si>
+    <t>Manager 2</t>
+  </si>
+  <si>
+    <t>Manager 3</t>
+  </si>
+  <si>
+    <t>Manager 4</t>
+  </si>
+  <si>
+    <t>Manager 5</t>
+  </si>
+  <si>
+    <t>Manager 6</t>
+  </si>
+  <si>
+    <t>Manager 7</t>
+  </si>
+  <si>
+    <t>Manager 8</t>
+  </si>
+  <si>
+    <t>Project 1</t>
+  </si>
+  <si>
+    <t>Project 2</t>
+  </si>
+  <si>
+    <t>Project 3</t>
+  </si>
+  <si>
+    <t>Project 4</t>
+  </si>
+  <si>
+    <t>Project 5</t>
+  </si>
+  <si>
+    <t>Project 6</t>
+  </si>
+  <si>
+    <t>Project 7</t>
+  </si>
+  <si>
+    <t>Project 8</t>
+  </si>
+  <si>
+    <t>Project 9</t>
+  </si>
+  <si>
+    <t>Project 10</t>
+  </si>
+  <si>
+    <t>Project 11</t>
+  </si>
+  <si>
+    <t>Project 12</t>
+  </si>
+  <si>
+    <t>Total Managers :</t>
+  </si>
+  <si>
+    <t>LHS</t>
+  </si>
+  <si>
+    <t>Sign</t>
+  </si>
+  <si>
+    <t>RHS</t>
+  </si>
+  <si>
+    <t>&lt;=</t>
+  </si>
+  <si>
+    <t>=</t>
+  </si>
 </sst>
 </file>
 
@@ -240,7 +365,7 @@
     <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="15">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -333,8 +458,23 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF0F1114"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF0F1114"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -389,8 +529,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="10">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -511,13 +657,74 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF404B61"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF404B61"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF404B61"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF404B61"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFE8EEF7"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFE8EEF7"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFE8EEF7"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFE8EEF7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF404B61"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF404B61"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFE8EEF7"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFE8EEF7"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFE8EEF7"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
@@ -586,6 +793,33 @@
     <xf numFmtId="9" fontId="12" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -941,13 +1175,13 @@
                 <c:formatCode>_("$"* #,##0_);_("$"* \(#,##0\);_("$"* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>1518</c:v>
+                  <c:v>2318</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1302</c:v>
+                  <c:v>2002</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>986</c:v>
+                  <c:v>1586</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1009,13 +1243,13 @@
                 <c:formatCode>_("$"* #,##0_);_("$"* \(#,##0\);_("$"* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>1850</c:v>
+                  <c:v>350</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>650</c:v>
+                  <c:v>250</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>550</c:v>
+                  <c:v>150</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1914,13 +2148,13 @@
                 <c:formatCode>_("$"* #,##0_);_("$"* \(#,##0\);_("$"* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>1518</c:v>
+                  <c:v>2318</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1302</c:v>
+                  <c:v>2002</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>986</c:v>
+                  <c:v>1586</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2346,13 +2580,13 @@
                 <c:formatCode>_("$"* #,##0_);_("$"* \(#,##0\);_("$"* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>1850</c:v>
+                  <c:v>350</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>650</c:v>
+                  <c:v>250</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>550</c:v>
+                  <c:v>150</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5596,7 +5830,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7470FA0B-B6E7-45D6-BAB6-F3953091B4B4}">
-  <dimension ref="A1:Q49"/>
+  <dimension ref="A1:Q79"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
@@ -5606,9 +5840,9 @@
     <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.69921875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11.796875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.59765625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9.8984375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.19921875" customWidth="1"/>
+    <col min="10" max="10" width="8.59765625" customWidth="1"/>
     <col min="11" max="11" width="14.69921875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="9.69921875" customWidth="1"/>
     <col min="13" max="13" width="34" bestFit="1" customWidth="1"/>
@@ -5618,20 +5852,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="21">
-      <c r="A1" s="52" t="s">
+      <c r="A1" s="61" t="s">
         <v>46</v>
       </c>
-      <c r="B1" s="53"/>
-      <c r="C1" s="53"/>
-      <c r="D1" s="53"/>
-      <c r="E1" s="53"/>
-      <c r="F1" s="53"/>
-      <c r="G1" s="53"/>
-      <c r="H1" s="53"/>
-      <c r="I1" s="53"/>
-      <c r="J1" s="53"/>
-      <c r="K1" s="53"/>
-      <c r="L1" s="53"/>
+      <c r="B1" s="62"/>
+      <c r="C1" s="62"/>
+      <c r="D1" s="62"/>
+      <c r="E1" s="62"/>
+      <c r="F1" s="62"/>
+      <c r="G1" s="62"/>
+      <c r="H1" s="62"/>
+      <c r="I1" s="62"/>
+      <c r="J1" s="62"/>
+      <c r="K1" s="62"/>
+      <c r="L1" s="62"/>
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="15" t="s">
@@ -5662,10 +5896,10 @@
       </c>
       <c r="I3" s="15"/>
       <c r="J3" s="15"/>
-      <c r="M3" s="54" t="s">
+      <c r="M3" s="63" t="s">
         <v>22</v>
       </c>
-      <c r="N3" s="54"/>
+      <c r="N3" s="63"/>
     </row>
     <row r="4" spans="1:16" ht="20.399999999999999">
       <c r="B4" s="22">
@@ -5829,10 +6063,10 @@
       <c r="H9" s="25">
         <v>180</v>
       </c>
-      <c r="M9" s="56" t="s">
+      <c r="M9" s="65" t="s">
         <v>12</v>
       </c>
-      <c r="N9" s="57"/>
+      <c r="N9" s="66"/>
     </row>
     <row r="10" spans="1:16">
       <c r="B10" s="24">
@@ -5861,7 +6095,7 @@
       </c>
       <c r="N10" s="38">
         <f>IF(D38&lt;4000,1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -5951,7 +6185,7 @@
       </c>
       <c r="N13" s="38">
         <f>IF(G38&lt;10000,1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -6022,23 +6256,23 @@
       </c>
       <c r="N16" s="38">
         <f>SUM(K26:K29)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O16" s="44"/>
     </row>
     <row r="17" spans="1:17">
-      <c r="D17" s="59" t="s">
+      <c r="D17" s="68" t="s">
         <v>50</v>
       </c>
-      <c r="E17" s="59"/>
-      <c r="F17" s="59"/>
-      <c r="G17" s="59"/>
+      <c r="E17" s="68"/>
+      <c r="F17" s="68"/>
+      <c r="G17" s="68"/>
       <c r="M17" s="38" t="s">
         <v>28</v>
       </c>
       <c r="N17" s="38">
         <f>SUM(K32:K34)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O17" s="44"/>
     </row>
@@ -6172,7 +6406,7 @@
       </c>
       <c r="N20" s="19">
         <f>IF(SUM(N10:N14)=5,1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:17">
@@ -6322,11 +6556,11 @@
         <v>3313</v>
       </c>
       <c r="K24" s="44"/>
-      <c r="O24" s="51" t="s">
+      <c r="O24" s="60" t="s">
         <v>41</v>
       </c>
-      <c r="P24" s="51"/>
-      <c r="Q24" s="51"/>
+      <c r="P24" s="60"/>
+      <c r="Q24" s="60"/>
     </row>
     <row r="25" spans="1:17">
       <c r="K25" s="44"/>
@@ -6382,7 +6616,7 @@
       <c r="K26" s="50">
         <v>1</v>
       </c>
-      <c r="M26" s="58" t="s">
+      <c r="M26" s="67" t="s">
         <v>45</v>
       </c>
       <c r="N26" s="46" t="s">
@@ -6442,21 +6676,21 @@
       <c r="K27" s="50">
         <v>1</v>
       </c>
-      <c r="M27" s="58"/>
+      <c r="M27" s="67"/>
       <c r="N27" s="46" t="s">
         <v>9</v>
       </c>
       <c r="O27" s="36">
         <f>D30</f>
-        <v>1518</v>
+        <v>2318</v>
       </c>
       <c r="P27" s="36">
         <f>E30</f>
-        <v>1302</v>
+        <v>2002</v>
       </c>
       <c r="Q27" s="36">
         <f>F30</f>
-        <v>986</v>
+        <v>1586</v>
       </c>
     </row>
     <row r="28" spans="1:17">
@@ -6493,28 +6727,28 @@
         <f t="shared" si="8"/>
         <v>246.4</v>
       </c>
-      <c r="J28" s="2" t="str">
+      <c r="J28" s="2">
         <f t="shared" si="9"/>
-        <v/>
+        <v>0.11733333333333333</v>
       </c>
       <c r="K28" s="50">
-        <v>0</v>
-      </c>
-      <c r="M28" s="58"/>
+        <v>1</v>
+      </c>
+      <c r="M28" s="67"/>
       <c r="N28" s="46" t="s">
         <v>10</v>
       </c>
       <c r="O28" s="36">
         <f>D35</f>
-        <v>1850</v>
+        <v>350</v>
       </c>
       <c r="P28" s="36">
         <f>E35</f>
-        <v>650</v>
+        <v>250</v>
       </c>
       <c r="Q28" s="36">
         <f>F35</f>
-        <v>550</v>
+        <v>150</v>
       </c>
     </row>
     <row r="29" spans="1:17">
@@ -6565,19 +6799,19 @@
       </c>
       <c r="D30" s="43">
         <f>SUMPRODUCT(D26:D29,$K$26:$K$29)</f>
-        <v>1518</v>
+        <v>2318</v>
       </c>
       <c r="E30" s="43">
         <f t="shared" ref="E30:F30" si="10">SUMPRODUCT(E26:E29,$K$26:$K$29)</f>
-        <v>1302</v>
+        <v>2002</v>
       </c>
       <c r="F30" s="43">
         <f t="shared" si="10"/>
-        <v>986</v>
+        <v>1586</v>
       </c>
       <c r="G30" s="36">
         <f>SUM(D30:F30)</f>
-        <v>3806</v>
+        <v>5906</v>
       </c>
       <c r="K30" s="44"/>
     </row>
@@ -6702,12 +6936,12 @@
         <f>H34*(1-$N$7)</f>
         <v>299.2</v>
       </c>
-      <c r="J34" s="2">
+      <c r="J34" s="2" t="str">
         <f t="shared" si="13"/>
-        <v>0.13008695652173913</v>
+        <v/>
       </c>
       <c r="K34" s="50">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:11">
@@ -6716,19 +6950,19 @@
       </c>
       <c r="D35" s="5">
         <f>SUMPRODUCT(D32:D34,$K$32:$K$34)</f>
-        <v>1850</v>
+        <v>350</v>
       </c>
       <c r="E35" s="5">
         <f t="shared" ref="E35:F35" si="14">SUMPRODUCT(E32:E34,$K$32:$K$34)</f>
-        <v>650</v>
+        <v>250</v>
       </c>
       <c r="F35" s="5">
         <f t="shared" si="14"/>
-        <v>550</v>
+        <v>150</v>
       </c>
       <c r="G35" s="5">
         <f>SUM(D35:F35)</f>
-        <v>3050</v>
+        <v>750</v>
       </c>
     </row>
     <row r="36" spans="1:11">
@@ -6758,31 +6992,31 @@
       </c>
       <c r="D38" s="14">
         <f>SUMPRODUCT(D19:D23,$K$19:$K$23)+SUMPRODUCT(D26:D29,$K$26:$K$29)+SUMPRODUCT(D32:D34,$K$32:$K$34)</f>
-        <v>4483</v>
+        <v>3783</v>
       </c>
       <c r="E38" s="14">
         <f>SUMPRODUCT(E19:E23,$K$19:$K$23)+SUMPRODUCT(E26:E29,$K$26:$K$29)+SUMPRODUCT(E32:E34,$K$32:$K$34)</f>
-        <v>2951</v>
+        <v>3251</v>
       </c>
       <c r="F38" s="14">
         <f t="shared" ref="F38" si="15">SUMPRODUCT(F19:F23,$K$19:$K$23)+SUMPRODUCT(F26:F29,$K$26:$K$29)+SUMPRODUCT(F32:F34,$K$32:$K$34)</f>
-        <v>2735</v>
+        <v>2935</v>
       </c>
       <c r="G38" s="14">
         <f>SUM(D38:F38)</f>
-        <v>10169</v>
+        <v>9969</v>
       </c>
       <c r="I38" s="48">
         <f>SUMPRODUCT(I19:I34,K19:K34)</f>
-        <v>2076.8000000000002</v>
+        <v>2024.0000000000002</v>
       </c>
     </row>
     <row r="40" spans="1:11">
-      <c r="E40" s="55" t="s">
+      <c r="E40" s="64" t="s">
         <v>32</v>
       </c>
-      <c r="F40" s="55"/>
-      <c r="G40" s="55"/>
+      <c r="F40" s="64"/>
+      <c r="G40" s="64"/>
     </row>
     <row r="41" spans="1:11">
       <c r="D41" s="12" t="s">
@@ -6802,7 +7036,7 @@
       <c r="D42" s="40"/>
       <c r="E42" s="42">
         <f>AVERAGE(J19:J34)</f>
-        <v>0.14741107277049306</v>
+        <v>0.14599400352733688</v>
       </c>
       <c r="F42" s="42">
         <f>MIN(J19:J34)</f>
@@ -6819,7 +7053,7 @@
       </c>
       <c r="E43" s="2">
         <f t="dataTable" ref="E43:G49" dt2D="0" dtr="0" r1="N7"/>
-        <v>0.16751258269374214</v>
+        <v>0.16590227673561009</v>
       </c>
       <c r="F43" s="2">
         <v>0.1125</v>
@@ -6833,7 +7067,7 @@
         <v>0.05</v>
       </c>
       <c r="E44" s="2">
-        <v>0.15913695355905499</v>
+        <v>0.15760716289882956</v>
       </c>
       <c r="F44" s="2">
         <v>0.106875</v>
@@ -6847,7 +7081,7 @@
         <v>0.1</v>
       </c>
       <c r="E45" s="2">
-        <v>0.1507613244243679</v>
+        <v>0.14931204906204906</v>
       </c>
       <c r="F45" s="2">
         <v>0.10125000000000001</v>
@@ -6861,7 +7095,7 @@
         <v>0.15</v>
       </c>
       <c r="E46" s="2">
-        <v>0.14238569528968081</v>
+        <v>0.14101693522526856</v>
       </c>
       <c r="F46" s="2">
         <v>9.5625000000000002E-2</v>
@@ -6875,7 +7109,7 @@
         <v>0.2</v>
       </c>
       <c r="E47" s="2">
-        <v>0.1340100661549937</v>
+        <v>0.13272182138848806</v>
       </c>
       <c r="F47" s="2">
         <v>0.09</v>
@@ -6889,7 +7123,7 @@
         <v>0.25</v>
       </c>
       <c r="E48" s="2">
-        <v>0.12563443702030658</v>
+        <v>0.12442670755170754</v>
       </c>
       <c r="F48" s="2">
         <v>8.4375000000000006E-2</v>
@@ -6898,18 +7132,627 @@
         <v>0.17083333333333334</v>
       </c>
     </row>
-    <row r="49" spans="4:7">
+    <row r="49" spans="2:13">
       <c r="D49" s="2">
         <v>0.3</v>
       </c>
       <c r="E49" s="2">
-        <v>0.11725880788561947</v>
+        <v>0.11613159371492705</v>
       </c>
       <c r="F49" s="2">
         <v>7.8749999999999987E-2</v>
       </c>
       <c r="G49" s="2">
         <v>0.15944444444444444</v>
+      </c>
+    </row>
+    <row r="58" spans="2:13" ht="16.2" thickBot="1"/>
+    <row r="59" spans="2:13" ht="16.2" thickBot="1">
+      <c r="B59" s="52"/>
+      <c r="C59" s="53" t="s">
+        <v>52</v>
+      </c>
+      <c r="D59" s="53" t="s">
+        <v>53</v>
+      </c>
+      <c r="E59" s="53" t="s">
+        <v>54</v>
+      </c>
+      <c r="F59" s="53" t="s">
+        <v>55</v>
+      </c>
+      <c r="G59" s="53" t="s">
+        <v>56</v>
+      </c>
+      <c r="H59" s="53" t="s">
+        <v>57</v>
+      </c>
+      <c r="I59" s="53" t="s">
+        <v>58</v>
+      </c>
+      <c r="J59" s="53" t="s">
+        <v>59</v>
+      </c>
+      <c r="K59" s="56" t="s">
+        <v>73</v>
+      </c>
+      <c r="L59" s="56" t="s">
+        <v>74</v>
+      </c>
+      <c r="M59" s="56" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="60" spans="2:13" ht="16.2" thickBot="1">
+      <c r="B60" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="C60" s="54">
+        <v>1</v>
+      </c>
+      <c r="D60" s="54">
+        <v>0</v>
+      </c>
+      <c r="E60" s="54">
+        <v>0</v>
+      </c>
+      <c r="F60" s="54">
+        <v>0</v>
+      </c>
+      <c r="G60" s="54">
+        <v>0</v>
+      </c>
+      <c r="H60" s="54">
+        <v>0</v>
+      </c>
+      <c r="I60" s="54">
+        <v>0</v>
+      </c>
+      <c r="J60" s="54">
+        <v>0</v>
+      </c>
+      <c r="K60" s="57">
+        <f>SUM(C60:J60)*K19</f>
+        <v>0</v>
+      </c>
+      <c r="L60" t="s">
+        <v>76</v>
+      </c>
+      <c r="M60">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="2:13" ht="16.2" thickBot="1">
+      <c r="B61" s="51" t="s">
+        <v>61</v>
+      </c>
+      <c r="C61" s="54">
+        <v>0</v>
+      </c>
+      <c r="D61" s="54">
+        <v>1</v>
+      </c>
+      <c r="E61" s="54">
+        <v>0</v>
+      </c>
+      <c r="F61" s="54">
+        <v>0</v>
+      </c>
+      <c r="G61" s="54">
+        <v>0</v>
+      </c>
+      <c r="H61" s="54">
+        <v>0</v>
+      </c>
+      <c r="I61" s="54">
+        <v>0</v>
+      </c>
+      <c r="J61" s="54">
+        <v>0</v>
+      </c>
+      <c r="K61" s="57">
+        <f t="shared" ref="K61:K64" si="16">SUM(C61:J61)*K20</f>
+        <v>1</v>
+      </c>
+      <c r="L61" t="s">
+        <v>76</v>
+      </c>
+      <c r="M61">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="2:13" ht="16.2" thickBot="1">
+      <c r="B62" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="C62" s="54">
+        <v>0</v>
+      </c>
+      <c r="D62" s="54">
+        <v>0</v>
+      </c>
+      <c r="E62" s="54">
+        <v>1</v>
+      </c>
+      <c r="F62" s="54">
+        <v>0</v>
+      </c>
+      <c r="G62" s="54">
+        <v>0</v>
+      </c>
+      <c r="H62" s="54">
+        <v>0</v>
+      </c>
+      <c r="I62" s="54">
+        <v>0</v>
+      </c>
+      <c r="J62" s="54">
+        <v>0</v>
+      </c>
+      <c r="K62" s="57">
+        <f t="shared" si="16"/>
+        <v>1</v>
+      </c>
+      <c r="L62" t="s">
+        <v>76</v>
+      </c>
+      <c r="M62">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="2:13" ht="16.2" thickBot="1">
+      <c r="B63" s="51" t="s">
+        <v>63</v>
+      </c>
+      <c r="C63" s="54">
+        <v>0</v>
+      </c>
+      <c r="D63" s="54">
+        <v>0</v>
+      </c>
+      <c r="E63" s="54">
+        <v>0</v>
+      </c>
+      <c r="F63" s="54">
+        <v>1</v>
+      </c>
+      <c r="G63" s="54">
+        <v>0</v>
+      </c>
+      <c r="H63" s="54">
+        <v>0</v>
+      </c>
+      <c r="I63" s="54">
+        <v>0</v>
+      </c>
+      <c r="J63" s="54">
+        <v>0</v>
+      </c>
+      <c r="K63" s="57">
+        <f t="shared" si="16"/>
+        <v>1</v>
+      </c>
+      <c r="L63" t="s">
+        <v>76</v>
+      </c>
+      <c r="M63">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="2:13" ht="16.2" thickBot="1">
+      <c r="B64" s="51" t="s">
+        <v>64</v>
+      </c>
+      <c r="C64" s="54">
+        <v>0</v>
+      </c>
+      <c r="D64" s="54">
+        <v>0</v>
+      </c>
+      <c r="E64" s="54">
+        <v>0</v>
+      </c>
+      <c r="F64" s="54">
+        <v>0</v>
+      </c>
+      <c r="G64" s="54">
+        <v>1</v>
+      </c>
+      <c r="H64" s="54">
+        <v>0</v>
+      </c>
+      <c r="I64" s="54">
+        <v>0</v>
+      </c>
+      <c r="J64" s="54">
+        <v>0</v>
+      </c>
+      <c r="K64" s="57">
+        <f t="shared" si="16"/>
+        <v>1</v>
+      </c>
+      <c r="L64" t="s">
+        <v>76</v>
+      </c>
+      <c r="M64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="2:13" ht="16.2" thickBot="1">
+      <c r="B65" s="51" t="s">
+        <v>65</v>
+      </c>
+      <c r="C65" s="54">
+        <v>0</v>
+      </c>
+      <c r="D65" s="54">
+        <v>0</v>
+      </c>
+      <c r="E65" s="54">
+        <v>0</v>
+      </c>
+      <c r="F65" s="54">
+        <v>0</v>
+      </c>
+      <c r="G65" s="54">
+        <v>0</v>
+      </c>
+      <c r="H65" s="54">
+        <v>1</v>
+      </c>
+      <c r="I65" s="54">
+        <v>0</v>
+      </c>
+      <c r="J65" s="54">
+        <v>0</v>
+      </c>
+      <c r="K65" s="57">
+        <f>SUM(C65:J65)*K26</f>
+        <v>1</v>
+      </c>
+      <c r="L65" t="s">
+        <v>76</v>
+      </c>
+      <c r="M65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="2:13" ht="16.2" thickBot="1">
+      <c r="B66" s="51" t="s">
+        <v>66</v>
+      </c>
+      <c r="C66" s="54">
+        <v>0</v>
+      </c>
+      <c r="D66" s="54">
+        <v>0</v>
+      </c>
+      <c r="E66" s="54">
+        <v>0</v>
+      </c>
+      <c r="F66" s="54">
+        <v>0</v>
+      </c>
+      <c r="G66" s="54">
+        <v>0</v>
+      </c>
+      <c r="H66" s="54">
+        <v>0</v>
+      </c>
+      <c r="I66" s="54">
+        <v>1</v>
+      </c>
+      <c r="J66" s="54">
+        <v>0</v>
+      </c>
+      <c r="K66" s="57">
+        <f t="shared" ref="K66:K68" si="17">SUM(C66:J66)*K27</f>
+        <v>1</v>
+      </c>
+      <c r="L66" t="s">
+        <v>76</v>
+      </c>
+      <c r="M66">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="2:13" ht="16.2" thickBot="1">
+      <c r="B67" s="51" t="s">
+        <v>67</v>
+      </c>
+      <c r="C67" s="54">
+        <v>0</v>
+      </c>
+      <c r="D67" s="54">
+        <v>0</v>
+      </c>
+      <c r="E67" s="54">
+        <v>0</v>
+      </c>
+      <c r="F67" s="54">
+        <v>0</v>
+      </c>
+      <c r="G67" s="54">
+        <v>0</v>
+      </c>
+      <c r="H67" s="54">
+        <v>0</v>
+      </c>
+      <c r="I67" s="54">
+        <v>0</v>
+      </c>
+      <c r="J67" s="54">
+        <v>0</v>
+      </c>
+      <c r="K67" s="57">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="L67" t="s">
+        <v>76</v>
+      </c>
+      <c r="M67">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="2:13" ht="16.2" thickBot="1">
+      <c r="B68" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="C68" s="54">
+        <v>0</v>
+      </c>
+      <c r="D68" s="54">
+        <v>0</v>
+      </c>
+      <c r="E68" s="54">
+        <v>0</v>
+      </c>
+      <c r="F68" s="54">
+        <v>0</v>
+      </c>
+      <c r="G68" s="54">
+        <v>0</v>
+      </c>
+      <c r="H68" s="54">
+        <v>0</v>
+      </c>
+      <c r="I68" s="54">
+        <v>0</v>
+      </c>
+      <c r="J68" s="54">
+        <v>0</v>
+      </c>
+      <c r="K68" s="57">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="L68" t="s">
+        <v>76</v>
+      </c>
+      <c r="M68">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="2:13" ht="16.2" thickBot="1">
+      <c r="B69" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="C69" s="54">
+        <v>0</v>
+      </c>
+      <c r="D69" s="54">
+        <v>0</v>
+      </c>
+      <c r="E69" s="54">
+        <v>0</v>
+      </c>
+      <c r="F69" s="54">
+        <v>0</v>
+      </c>
+      <c r="G69" s="54">
+        <v>0</v>
+      </c>
+      <c r="H69" s="54">
+        <v>0</v>
+      </c>
+      <c r="I69" s="54">
+        <v>0</v>
+      </c>
+      <c r="J69" s="54">
+        <v>0</v>
+      </c>
+      <c r="K69" s="57">
+        <f>SUM(C69:J69)*K32</f>
+        <v>0</v>
+      </c>
+      <c r="L69" t="s">
+        <v>76</v>
+      </c>
+      <c r="M69">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="2:13" ht="16.2" thickBot="1">
+      <c r="B70" s="51" t="s">
+        <v>70</v>
+      </c>
+      <c r="C70" s="54">
+        <v>0</v>
+      </c>
+      <c r="D70" s="54">
+        <v>0</v>
+      </c>
+      <c r="E70" s="54">
+        <v>0</v>
+      </c>
+      <c r="F70" s="54">
+        <v>0</v>
+      </c>
+      <c r="G70" s="54">
+        <v>0</v>
+      </c>
+      <c r="H70" s="54">
+        <v>0</v>
+      </c>
+      <c r="I70" s="54">
+        <v>0</v>
+      </c>
+      <c r="J70" s="54">
+        <v>0</v>
+      </c>
+      <c r="K70" s="57">
+        <f t="shared" ref="K70:K71" si="18">SUM(C70:J70)*K33</f>
+        <v>0</v>
+      </c>
+      <c r="L70" t="s">
+        <v>76</v>
+      </c>
+      <c r="M70">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="2:13" ht="16.2" thickBot="1">
+      <c r="B71" s="51" t="s">
+        <v>71</v>
+      </c>
+      <c r="C71" s="54">
+        <v>0</v>
+      </c>
+      <c r="D71" s="54">
+        <v>0</v>
+      </c>
+      <c r="E71" s="54">
+        <v>0</v>
+      </c>
+      <c r="F71" s="54">
+        <v>0</v>
+      </c>
+      <c r="G71" s="54">
+        <v>0</v>
+      </c>
+      <c r="H71" s="54">
+        <v>0</v>
+      </c>
+      <c r="I71" s="54">
+        <v>0</v>
+      </c>
+      <c r="J71" s="54">
+        <v>1</v>
+      </c>
+      <c r="K71" s="57">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="L71" t="s">
+        <v>76</v>
+      </c>
+      <c r="M71">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="2:13">
+      <c r="B72" s="58" t="s">
+        <v>73</v>
+      </c>
+      <c r="C72" s="44">
+        <f>SUM(C60:C71)</f>
+        <v>1</v>
+      </c>
+      <c r="D72" s="44">
+        <f t="shared" ref="D72:J72" si="19">SUM(D60:D71)</f>
+        <v>1</v>
+      </c>
+      <c r="E72" s="44">
+        <f t="shared" si="19"/>
+        <v>1</v>
+      </c>
+      <c r="F72" s="44">
+        <f t="shared" si="19"/>
+        <v>1</v>
+      </c>
+      <c r="G72" s="44">
+        <f t="shared" si="19"/>
+        <v>1</v>
+      </c>
+      <c r="H72" s="44">
+        <f t="shared" si="19"/>
+        <v>1</v>
+      </c>
+      <c r="I72" s="44">
+        <f t="shared" si="19"/>
+        <v>1</v>
+      </c>
+      <c r="J72" s="44">
+        <f t="shared" si="19"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="2:13">
+      <c r="B73" s="58" t="s">
+        <v>74</v>
+      </c>
+      <c r="C73" s="44" t="s">
+        <v>77</v>
+      </c>
+      <c r="D73" s="44" t="s">
+        <v>77</v>
+      </c>
+      <c r="E73" s="44" t="s">
+        <v>77</v>
+      </c>
+      <c r="F73" s="44" t="s">
+        <v>77</v>
+      </c>
+      <c r="G73" s="44" t="s">
+        <v>77</v>
+      </c>
+      <c r="H73" s="44" t="s">
+        <v>77</v>
+      </c>
+      <c r="I73" s="44" t="s">
+        <v>77</v>
+      </c>
+      <c r="J73" s="44" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="74" spans="2:13">
+      <c r="B74" s="58" t="s">
+        <v>75</v>
+      </c>
+      <c r="C74" s="59">
+        <v>1</v>
+      </c>
+      <c r="D74" s="59">
+        <v>1</v>
+      </c>
+      <c r="E74" s="59">
+        <v>1</v>
+      </c>
+      <c r="F74" s="59">
+        <v>1</v>
+      </c>
+      <c r="G74" s="59">
+        <v>1</v>
+      </c>
+      <c r="H74" s="59">
+        <v>1</v>
+      </c>
+      <c r="I74" s="59">
+        <v>1</v>
+      </c>
+      <c r="J74" s="59">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="2:13" ht="27.6">
+      <c r="B79" s="55" t="s">
+        <v>72</v>
+      </c>
+      <c r="C79">
+        <f>SUM(C60:J71)</f>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
